--- a/_data/Syllabus.xlsx
+++ b/_data/Syllabus.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/grysli01/personalRepos/cse2321/_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/grysli01/osu_repos/cse2321/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2846D652-5D4A-3448-A582-1AC578A8135A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98E88FC-3296-4C4C-A1E1-596863C97AE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="19800" windowHeight="18000" xr2:uid="{DE38FA10-6465-D545-92BA-8AB89C1CB985}"/>
+    <workbookView xWindow="-39560" yWindow="-6000" windowWidth="48240" windowHeight="22440" xr2:uid="{DE38FA10-6465-D545-92BA-8AB89C1CB985}"/>
   </bookViews>
   <sheets>
     <sheet name="Syllabus" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="53">
   <si>
     <t>Class</t>
   </si>
@@ -140,56 +140,62 @@
     <t>HW 10</t>
   </si>
   <si>
-    <t>&lt;a href= "https://osu.instructure.com/courses/205581/assignments/5234201"&gt; HW1 &lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>&lt;a href= "https://osu.instructure.com/courses/205581/assignments/5234203"&gt; HW2 &lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>&lt;a href= "https://osu.instructure.com/courses/205581/assignments/5234204"&gt; HW3 &lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>&lt;a href= "https://osu.instructure.com/courses/205581/assignments/5234205"&gt; HW4 &lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>&lt;a href= "https://osu.instructure.com/courses/205581/assignments/5234206"&gt; HW5 &lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>&lt;a href= "https://osu.instructure.com/courses/205581/assignments/5234207"&gt; HW6 &lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>&lt;a href= "https://osu.instructure.com/courses/205581/assignments/5234208"&gt; HW7 &lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>&lt;a href= "https://osu.instructure.com/courses/205581/assignments/5234209"&gt; HW8&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>&lt;a href= "https://osu.instructure.com/courses/205581/assignments/5234210"&gt; HW9&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>&lt;a href= "https://osu.instructure.com/courses/205581/assignments/5234202"&gt; HW10&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>1. &lt;a href =  "https://osu.instructure.com/files/85722265"&gt; Logic 1  &lt;/a&gt; &lt;br&gt; 
-2. &lt;a href =  "https://osu.instructure.com/files/85722294"&gt; Logic 2 &lt;/a&gt; &lt;br&gt;
-3. &lt;a href =  "https://osu.instructure.com/files/85722266"&gt; Proof Methods &lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>1. &lt;a href =  "https://osu.instructure.com/files/85722267"&gt; Set Theory 1  &lt;/a&gt; &lt;br&gt; 
-2. &lt;a href =  "https://osu.instructure.com/files/85722288"&gt; Set Theory 2 &lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>1. &lt;a href ="https://osu.instructure.com/files/85722281"&gt; Algorithms  &lt;/a&gt; &lt;br&gt; 
-2. &lt;a href =  "https://osu.instructure.com/files/85722270"&gt; Asymptotic Behavior &lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>1. &lt;a href ="https://osu.instructure.com/files/85722295"&gt; Induction  &lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>1. &lt;a href =  "https://osu.instructure.com/files/85722276"&gt; Recursion &lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>1. &lt;a href =  "https://osu.instructure.com/files/85722296"&gt; Graph Algorithms&lt;/a&gt;</t>
+    <t>&lt;a href= "https://osu.instructure.com/courses/219401/assignments/5635928"&gt; HW1 &lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a href= "https://osu.instructure.com/courses/219401/assignments/5635931"&gt; HW2 &lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a href= "https://osu.instructure.com/courses/219401/assignments/5635932"&gt; HW3 &lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a href= "https://osu.instructure.com/courses/219401/assignments/5635933"&gt; HW4 &lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a href= "https://osu.instructure.com/courses/219401/assignments/5635935"&gt; HW5 &lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a href= "https://osu.instructure.com/courses/219401/assignments/5635936"&gt; HW6 &lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a href= "https://osu.instructure.com/courses/219401/assignments/5635937"&gt; HW7 &lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a href= "https://osu.instructure.com/courses/219401/assignments/5635939"&gt; HW8&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a href= "https://osu.instructure.com/courses/219401/assignments/5635940"&gt; HW9&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a href= "https://osu.instructure.com/courses/219401/assignments/5635929"&gt; HW10&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>1. &lt;a href =  "https://osu.instructure.com/files/91952911"&gt; Logic 1  &lt;/a&gt; &lt;br&gt; 
+2. &lt;a href =  "https://osu.instructure.com/files/91952938"&gt; Logic 2 &lt;/a&gt; &lt;br&gt;
+3. &lt;a href =  "https://osu.instructure.com/files/91952917"&gt; Proof Methods &lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>1. &lt;a href =  "https://osu.instructure.com/files/91952918"&gt; Set Theory 1  &lt;/a&gt; &lt;br&gt; 
+2. &lt;a href =  "https://osu.instructure.com/files/91952932"&gt; Set Theory 2 &lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>1. &lt;a href ="https://osu.instructure.com/files/91952933"&gt; Algorithms  &lt;/a&gt; &lt;br&gt; 
+2. &lt;a href =  "https://osu.instructure.com/files/91952919"&gt; Asymptotic Behavior &lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>1. &lt;a href ="https://osu.instructure.com/files/91952939"&gt; Induction  &lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>1. &lt;a href =  "https://osu.instructure.com/files/91952923"&gt; Recursion &lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>1. &lt;a href =  "https://osu.instructure.com/files/91952940"&gt; Graph Algorithms&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>Autum Break</t>
+  </si>
+  <si>
+    <t>Thanksgiving</t>
   </si>
 </sst>
 </file>
@@ -1060,8 +1066,8 @@
     <col min="3" max="3" width="8.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.33203125" customWidth="1"/>
     <col min="5" max="5" width="27.6640625" customWidth="1"/>
-    <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="55.1640625" customWidth="1"/>
+    <col min="6" max="6" width="85.33203125" customWidth="1"/>
+    <col min="7" max="7" width="8.1640625" customWidth="1"/>
     <col min="8" max="8" width="66.6640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1106,11 +1112,11 @@
         <v>1</v>
       </c>
       <c r="C2" s="2">
-        <v>46034</v>
+        <v>46259</v>
       </c>
       <c r="D2" t="str">
         <f>TEXT(C2,"ddd")</f>
-        <v>Mon</v>
+        <v>Tue</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -1128,11 +1134,11 @@
       </c>
       <c r="C3" s="2">
         <f>IF(MOD(A3,2)=0,C2+2,C2+5)</f>
-        <v>46036</v>
+        <v>46261</v>
       </c>
       <c r="D3" t="str">
         <f t="shared" ref="D3:D32" si="0">TEXT(C3,"ddd")</f>
-        <v>Wed</v>
+        <v>Thu</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -1150,14 +1156,14 @@
       </c>
       <c r="C4" s="2">
         <f t="shared" ref="C4:C32" si="1">IF(MOD(A4,2)=0,C3+2,C3+5)</f>
-        <v>46041</v>
+        <v>46266</v>
       </c>
       <c r="D4" t="str">
         <f t="shared" si="0"/>
-        <v>Mon</v>
+        <v>Tue</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -1169,14 +1175,20 @@
       </c>
       <c r="C5" s="2">
         <f t="shared" si="1"/>
-        <v>46043</v>
+        <v>46268</v>
       </c>
       <c r="D5" t="str">
         <f t="shared" si="0"/>
-        <v>Wed</v>
+        <v>Thu</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -1188,20 +1200,14 @@
       </c>
       <c r="C6" s="2">
         <f t="shared" si="1"/>
-        <v>46048</v>
+        <v>46273</v>
       </c>
       <c r="D6" t="str">
         <f t="shared" si="0"/>
-        <v>Mon</v>
+        <v>Tue</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -1213,11 +1219,11 @@
       </c>
       <c r="C7" s="2">
         <f t="shared" si="1"/>
-        <v>46050</v>
+        <v>46275</v>
       </c>
       <c r="D7" t="str">
         <f t="shared" si="0"/>
-        <v>Wed</v>
+        <v>Thu</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
@@ -1232,11 +1238,11 @@
       </c>
       <c r="C8" s="2">
         <f t="shared" si="1"/>
-        <v>46055</v>
+        <v>46280</v>
       </c>
       <c r="D8" t="str">
         <f t="shared" si="0"/>
-        <v>Mon</v>
+        <v>Tue</v>
       </c>
       <c r="E8" t="s">
         <v>12</v>
@@ -1257,11 +1263,11 @@
       </c>
       <c r="C9" s="2">
         <f t="shared" si="1"/>
-        <v>46057</v>
+        <v>46282</v>
       </c>
       <c r="D9" t="str">
         <f t="shared" si="0"/>
-        <v>Wed</v>
+        <v>Thu</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
@@ -1279,11 +1285,11 @@
       </c>
       <c r="C10" s="2">
         <f t="shared" si="1"/>
-        <v>46062</v>
+        <v>46287</v>
       </c>
       <c r="D10" t="str">
         <f t="shared" si="0"/>
-        <v>Mon</v>
+        <v>Tue</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
@@ -1305,11 +1311,11 @@
       </c>
       <c r="C11" s="2">
         <f t="shared" si="1"/>
-        <v>46064</v>
+        <v>46289</v>
       </c>
       <c r="D11" t="str">
         <f t="shared" si="0"/>
-        <v>Wed</v>
+        <v>Thu</v>
       </c>
       <c r="E11" t="s">
         <v>16</v>
@@ -1325,11 +1331,11 @@
       </c>
       <c r="C12" s="2">
         <f t="shared" si="1"/>
-        <v>46069</v>
+        <v>46294</v>
       </c>
       <c r="D12" t="str">
         <f t="shared" si="0"/>
-        <v>Mon</v>
+        <v>Tue</v>
       </c>
       <c r="E12" t="s">
         <v>17</v>
@@ -1348,11 +1354,11 @@
       </c>
       <c r="C13" s="2">
         <f t="shared" si="1"/>
-        <v>46071</v>
+        <v>46296</v>
       </c>
       <c r="D13" t="str">
         <f t="shared" si="0"/>
-        <v>Wed</v>
+        <v>Thu</v>
       </c>
       <c r="E13" t="s">
         <v>18</v>
@@ -1371,11 +1377,11 @@
       </c>
       <c r="C14" s="2">
         <f t="shared" si="1"/>
-        <v>46076</v>
+        <v>46301</v>
       </c>
       <c r="D14" t="str">
         <f t="shared" si="0"/>
-        <v>Mon</v>
+        <v>Tue</v>
       </c>
       <c r="E14" t="s">
         <v>18</v>
@@ -1394,11 +1400,11 @@
       </c>
       <c r="C15" s="2">
         <f t="shared" si="1"/>
-        <v>46078</v>
+        <v>46303</v>
       </c>
       <c r="D15" t="str">
         <f t="shared" si="0"/>
-        <v>Wed</v>
+        <v>Thu</v>
       </c>
       <c r="E15" t="s">
         <v>18</v>
@@ -1414,11 +1420,11 @@
       </c>
       <c r="C16" s="2">
         <f t="shared" si="1"/>
-        <v>46083</v>
+        <v>46308</v>
       </c>
       <c r="D16" t="str">
         <f t="shared" si="0"/>
-        <v>Mon</v>
+        <v>Tue</v>
       </c>
       <c r="E16" t="s">
         <v>20</v>
@@ -1443,14 +1449,17 @@
       </c>
       <c r="C17" s="2">
         <f t="shared" si="1"/>
-        <v>46085</v>
+        <v>46310</v>
       </c>
       <c r="D17" t="str">
         <f t="shared" si="0"/>
-        <v>Wed</v>
+        <v>Thu</v>
       </c>
       <c r="E17" t="s">
-        <v>21</v>
+        <v>13</v>
+      </c>
+      <c r="H17" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
@@ -1463,20 +1472,14 @@
       </c>
       <c r="C18" s="2">
         <f t="shared" si="1"/>
-        <v>46090</v>
+        <v>46315</v>
       </c>
       <c r="D18" t="str">
         <f t="shared" si="0"/>
-        <v>Mon</v>
+        <v>Tue</v>
       </c>
       <c r="E18" t="s">
         <v>21</v>
-      </c>
-      <c r="F18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G18" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
@@ -1489,14 +1492,20 @@
       </c>
       <c r="C19" s="2">
         <f t="shared" si="1"/>
-        <v>46092</v>
+        <v>46317</v>
       </c>
       <c r="D19" t="str">
         <f t="shared" si="0"/>
-        <v>Wed</v>
+        <v>Thu</v>
       </c>
       <c r="E19" t="s">
         <v>21</v>
+      </c>
+      <c r="F19" t="s">
+        <v>41</v>
+      </c>
+      <c r="G19" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
@@ -1509,14 +1518,14 @@
       </c>
       <c r="C20" s="2">
         <f t="shared" si="1"/>
-        <v>46097</v>
+        <v>46322</v>
       </c>
       <c r="D20" t="str">
         <f t="shared" si="0"/>
-        <v>Mon</v>
+        <v>Tue</v>
       </c>
       <c r="E20" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
@@ -1529,14 +1538,23 @@
       </c>
       <c r="C21" s="2">
         <f t="shared" si="1"/>
-        <v>46099</v>
+        <v>46324</v>
       </c>
       <c r="D21" t="str">
         <f t="shared" si="0"/>
-        <v>Wed</v>
+        <v>Thu</v>
       </c>
       <c r="E21" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="G21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" t="s">
+        <v>49</v>
+      </c>
+      <c r="J21" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
@@ -1549,23 +1567,17 @@
       </c>
       <c r="C22" s="2">
         <f t="shared" si="1"/>
-        <v>46104</v>
+        <v>46329</v>
       </c>
       <c r="D22" t="str">
         <f t="shared" si="0"/>
-        <v>Mon</v>
+        <v>Tue</v>
       </c>
       <c r="E22" t="s">
         <v>23</v>
       </c>
-      <c r="G22" t="s">
-        <v>26</v>
-      </c>
-      <c r="H22" t="s">
-        <v>49</v>
-      </c>
-      <c r="J22" t="s">
-        <v>25</v>
+      <c r="F22" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
@@ -1578,17 +1590,14 @@
       </c>
       <c r="C23" s="2">
         <f t="shared" si="1"/>
-        <v>46106</v>
+        <v>46331</v>
       </c>
       <c r="D23" t="str">
         <f t="shared" si="0"/>
-        <v>Wed</v>
+        <v>Thu</v>
       </c>
       <c r="E23" t="s">
         <v>23</v>
-      </c>
-      <c r="F23" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
@@ -1601,14 +1610,17 @@
       </c>
       <c r="C24" s="2">
         <f t="shared" si="1"/>
-        <v>46111</v>
+        <v>46336</v>
       </c>
       <c r="D24" t="str">
         <f t="shared" si="0"/>
-        <v>Mon</v>
+        <v>Tue</v>
       </c>
       <c r="E24" t="s">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="G24" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
@@ -1621,17 +1633,20 @@
       </c>
       <c r="C25" s="2">
         <f t="shared" si="1"/>
-        <v>46113</v>
+        <v>46338</v>
       </c>
       <c r="D25" t="str">
         <f t="shared" si="0"/>
-        <v>Wed</v>
+        <v>Thu</v>
       </c>
       <c r="E25" t="s">
-        <v>27</v>
-      </c>
-      <c r="G25" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="H25" t="s">
+        <v>50</v>
+      </c>
+      <c r="J25" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
@@ -1644,20 +1659,17 @@
       </c>
       <c r="C26" s="2">
         <f t="shared" si="1"/>
-        <v>46118</v>
+        <v>46343</v>
       </c>
       <c r="D26" t="str">
         <f t="shared" si="0"/>
-        <v>Mon</v>
+        <v>Tue</v>
       </c>
       <c r="E26" t="s">
-        <v>28</v>
-      </c>
-      <c r="H26" t="s">
-        <v>50</v>
-      </c>
-      <c r="J26" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="F26" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
@@ -1670,17 +1682,17 @@
       </c>
       <c r="C27" s="2">
         <f t="shared" si="1"/>
-        <v>46120</v>
+        <v>46345</v>
       </c>
       <c r="D27" t="str">
         <f t="shared" si="0"/>
-        <v>Wed</v>
+        <v>Thu</v>
       </c>
       <c r="E27" t="s">
         <v>29</v>
       </c>
-      <c r="F27" t="s">
-        <v>43</v>
+      <c r="G27" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
@@ -1693,17 +1705,17 @@
       </c>
       <c r="C28" s="2">
         <f t="shared" si="1"/>
-        <v>46125</v>
+        <v>46350</v>
       </c>
       <c r="D28" t="str">
         <f t="shared" si="0"/>
-        <v>Mon</v>
+        <v>Tue</v>
       </c>
       <c r="E28" t="s">
         <v>29</v>
       </c>
-      <c r="G28" t="s">
-        <v>32</v>
+      <c r="F28" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
@@ -1716,17 +1728,17 @@
       </c>
       <c r="C29" s="2">
         <f t="shared" si="1"/>
-        <v>46127</v>
+        <v>46352</v>
       </c>
       <c r="D29" t="str">
         <f t="shared" si="0"/>
-        <v>Wed</v>
+        <v>Thu</v>
       </c>
       <c r="E29" t="s">
-        <v>29</v>
-      </c>
-      <c r="F29" t="s">
-        <v>44</v>
+        <v>13</v>
+      </c>
+      <c r="H29" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
@@ -1739,11 +1751,11 @@
       </c>
       <c r="C30" s="2">
         <f t="shared" si="1"/>
-        <v>46132</v>
+        <v>46357</v>
       </c>
       <c r="D30" t="str">
         <f t="shared" si="0"/>
-        <v>Mon</v>
+        <v>Tue</v>
       </c>
       <c r="E30" t="s">
         <v>29</v>
@@ -1759,11 +1771,11 @@
       </c>
       <c r="C31" s="2">
         <f t="shared" si="1"/>
-        <v>46134</v>
+        <v>46359</v>
       </c>
       <c r="D31" t="str">
         <f t="shared" si="0"/>
-        <v>Wed</v>
+        <v>Thu</v>
       </c>
       <c r="E31" t="s">
         <v>29</v>
@@ -1782,11 +1794,11 @@
       </c>
       <c r="C32" s="2">
         <f t="shared" si="1"/>
-        <v>46139</v>
+        <v>46364</v>
       </c>
       <c r="D32" t="str">
         <f t="shared" si="0"/>
-        <v>Mon</v>
+        <v>Tue</v>
       </c>
       <c r="E32" t="s">
         <v>33</v>

--- a/_data/Syllabus.xlsx
+++ b/_data/Syllabus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/grysli01/osu_repos/cse2321/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98E88FC-3296-4C4C-A1E1-596863C97AE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB87055-E0DF-8C46-86D5-28004BAEEE77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-39560" yWindow="-6000" windowWidth="48240" windowHeight="22440" xr2:uid="{DE38FA10-6465-D545-92BA-8AB89C1CB985}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17960" xr2:uid="{DE38FA10-6465-D545-92BA-8AB89C1CB985}"/>
   </bookViews>
   <sheets>
     <sheet name="Syllabus" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="54">
   <si>
     <t>Class</t>
   </si>
@@ -170,32 +170,35 @@
     <t>&lt;a href= "https://osu.instructure.com/courses/219401/assignments/5635929"&gt; HW10&lt;/a&gt;</t>
   </si>
   <si>
-    <t>1. &lt;a href =  "https://osu.instructure.com/files/91952911"&gt; Logic 1  &lt;/a&gt; &lt;br&gt; 
+    <t>1. &lt;a href =  "https://osu.instructure.com/files/91952918"&gt; Set Theory 1  &lt;/a&gt; &lt;br&gt; 
+2. &lt;a href =  "https://osu.instructure.com/files/91952932"&gt; Set Theory 2 &lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>1. &lt;a href ="https://osu.instructure.com/files/91952933"&gt; Algorithms  &lt;/a&gt; &lt;br&gt; 
+2. &lt;a href =  "https://osu.instructure.com/files/91952919"&gt; Asymptotic Behavior &lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>1. &lt;a href ="https://osu.instructure.com/files/91952939"&gt; Induction  &lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>1. &lt;a href =  "https://osu.instructure.com/files/91952923"&gt; Recursion &lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>1. &lt;a href =  "https://osu.instructure.com/files/91952940"&gt; Graph Algorithms&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>Autum Break</t>
+  </si>
+  <si>
+    <t>Thanksgiving</t>
+  </si>
+  <si>
+    <t>Misc topics</t>
+  </si>
+  <si>
+    <t>1. &lt;a href =  "/cse2321/course_materials/lectures/Logic1-GR.pdf"&gt; Logic 1  &lt;/a&gt; &lt;br&gt; 
 2. &lt;a href =  "https://osu.instructure.com/files/91952938"&gt; Logic 2 &lt;/a&gt; &lt;br&gt;
 3. &lt;a href =  "https://osu.instructure.com/files/91952917"&gt; Proof Methods &lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>1. &lt;a href =  "https://osu.instructure.com/files/91952918"&gt; Set Theory 1  &lt;/a&gt; &lt;br&gt; 
-2. &lt;a href =  "https://osu.instructure.com/files/91952932"&gt; Set Theory 2 &lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>1. &lt;a href ="https://osu.instructure.com/files/91952933"&gt; Algorithms  &lt;/a&gt; &lt;br&gt; 
-2. &lt;a href =  "https://osu.instructure.com/files/91952919"&gt; Asymptotic Behavior &lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>1. &lt;a href ="https://osu.instructure.com/files/91952939"&gt; Induction  &lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>1. &lt;a href =  "https://osu.instructure.com/files/91952923"&gt; Recursion &lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>1. &lt;a href =  "https://osu.instructure.com/files/91952940"&gt; Graph Algorithms&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t>Autum Break</t>
-  </si>
-  <si>
-    <t>Thanksgiving</t>
   </si>
 </sst>
 </file>
@@ -1066,9 +1069,10 @@
     <col min="3" max="3" width="8.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.33203125" customWidth="1"/>
     <col min="5" max="5" width="27.6640625" customWidth="1"/>
-    <col min="6" max="6" width="85.33203125" customWidth="1"/>
+    <col min="6" max="6" width="85" customWidth="1"/>
     <col min="7" max="7" width="8.1640625" customWidth="1"/>
     <col min="8" max="8" width="66.6640625" customWidth="1"/>
+    <col min="10" max="10" width="26.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
@@ -1122,7 +1126,7 @@
         <v>10</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -1273,7 +1277,7 @@
         <v>12</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -1364,7 +1368,7 @@
         <v>18</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -1436,7 +1440,7 @@
         <v>22</v>
       </c>
       <c r="H16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
@@ -1459,7 +1463,7 @@
         <v>13</v>
       </c>
       <c r="H17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
@@ -1551,7 +1555,7 @@
         <v>26</v>
       </c>
       <c r="H21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J21" t="s">
         <v>25</v>
@@ -1643,7 +1647,7 @@
         <v>28</v>
       </c>
       <c r="H25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J25" t="s">
         <v>31</v>
@@ -1738,7 +1742,7 @@
         <v>13</v>
       </c>
       <c r="H29" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
@@ -1778,7 +1782,7 @@
         <v>Thu</v>
       </c>
       <c r="E31" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="G31" t="s">
         <v>34</v>
